--- a/src/utils/athlete_import_example.xlsx
+++ b/src/utils/athlete_import_example.xlsx
@@ -448,7 +448,7 @@
         <v>bib_name</v>
       </c>
       <c r="J1" t="str">
-        <v>distance</v>
+        <v>category</v>
       </c>
       <c r="K1" t="str">
         <v>item</v>
@@ -679,7 +679,7 @@
         <v>Khong</v>
       </c>
       <c r="C8" t="str">
-        <v>Chuoi khung gio nhan (vd 08:00 - 10:00). Co the dung cot cu pickup_start + pickup_end (gio Excel Time / HH:mm) — se duoc ghep khi import.</v>
+        <v>Chuoi khung gio nhan (vd 08:00 - 10:00).</v>
       </c>
     </row>
     <row r="9">
@@ -701,7 +701,7 @@
         <v>Khong</v>
       </c>
       <c r="C10" t="str">
-        <v>email, phone, zone, bib, bib_name, distance, item, checkin_by...</v>
+        <v>email, phone, zone, bib, bib_name, category, item, checkin_by...</v>
       </c>
     </row>
   </sheetData>

--- a/src/utils/athlete_import_example.xlsx
+++ b/src/utils/athlete_import_example.xlsx
@@ -433,7 +433,7 @@
         <v>phone</v>
       </c>
       <c r="E1" t="str">
-        <v>dob(mm/dd/yyyy)</v>
+        <v>dob(yyyy-mm-dd)</v>
       </c>
       <c r="F1" t="str">
         <v>gender</v>
@@ -486,7 +486,7 @@
         <v>0909123456</v>
       </c>
       <c r="E2" t="str">
-        <v>03/15/1990</v>
+        <v>1990-03-15</v>
       </c>
       <c r="F2" t="str">
         <v>M</v>
@@ -539,7 +539,7 @@
         <v>0987654321</v>
       </c>
       <c r="E3" t="str">
-        <v>12/01/1995</v>
+        <v>1995-12-01</v>
       </c>
       <c r="F3" t="str">
         <v>F</v>
@@ -618,13 +618,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>dob(mm/dd/yyyy) hoac dob</v>
+        <v>dob(yyyy-mm-dd) hoac dob</v>
       </c>
       <c r="B3" t="str">
         <v>Khong</v>
       </c>
       <c r="C3" t="str">
-        <v>Ngay sinh; co the dung cot dob thay cho dob(mm/dd/yyyy).</v>
+        <v>Ngay sinh: chuoi yyyy-mm-dd hoac o Date trong Excel; khong dung text dang dd/mm/yyyy.</v>
       </c>
     </row>
     <row r="4">

--- a/src/utils/athlete_import_example.xlsx
+++ b/src/utils/athlete_import_example.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:R3"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -417,159 +417,166 @@
     <col min="15" max="15" width="16.83203125" customWidth="1"/>
     <col min="16" max="16" width="16.83203125" customWidth="1"/>
     <col min="17" max="17" width="16.83203125" customWidth="1"/>
+    <col min="18" max="18" width="16.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>bib</v>
+      </c>
+      <c r="B1" t="str">
+        <v>chip</v>
+      </c>
+      <c r="C1" t="str">
         <v>fullname</v>
       </c>
-      <c r="B1" t="str">
+      <c r="D1" t="str">
         <v>cccd</v>
       </c>
-      <c r="C1" t="str">
+      <c r="E1" t="str">
         <v>email</v>
       </c>
-      <c r="D1" t="str">
+      <c r="F1" t="str">
         <v>phone</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>dob(yyyy-mm-dd)</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>gender</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>zone</v>
       </c>
-      <c r="H1" t="str">
-        <v>bib</v>
-      </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>bib_name</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>category</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>item</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>qr_code</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>status</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>checkin_method</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>checkin_by</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Q1" t="str">
         <v>checkin_time</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="R1" t="str">
         <v>pickup_time_range</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>1001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>CHIP001</v>
+      </c>
+      <c r="C2" t="str">
         <v>Nguyen Van A</v>
       </c>
-      <c r="B2" t="str">
+      <c r="D2" t="str">
         <v>034085012345</v>
       </c>
-      <c r="C2" t="str">
+      <c r="E2" t="str">
         <v>nguyenvana@example.com</v>
       </c>
-      <c r="D2" t="str">
+      <c r="F2" t="str">
         <v>0909123456</v>
       </c>
-      <c r="E2" t="str">
+      <c r="G2" t="str">
         <v>1990-03-15</v>
       </c>
-      <c r="F2" t="str">
+      <c r="H2" t="str">
         <v>M</v>
       </c>
-      <c r="G2" t="str">
+      <c r="I2" t="str">
         <v>Khu A</v>
       </c>
-      <c r="H2" t="str">
-        <v>1001</v>
-      </c>
-      <c r="I2" t="str">
+      <c r="J2" t="str">
         <v>NVA-21K</v>
       </c>
-      <c r="J2" t="str">
+      <c r="K2" t="str">
         <v>21km</v>
       </c>
-      <c r="K2" t="str">
+      <c r="L2" t="str">
         <v>Ao size M</v>
       </c>
-      <c r="L2" t="str">
+      <c r="M2" t="str">
         <v/>
       </c>
-      <c r="M2" t="str">
+      <c r="N2" t="str">
         <v>registered</v>
       </c>
-      <c r="N2" t="str">
+      <c r="O2" t="str">
         <v>import</v>
-      </c>
-      <c r="O2" t="str">
-        <v/>
       </c>
       <c r="P2" t="str">
         <v/>
       </c>
       <c r="Q2" t="str">
+        <v/>
+      </c>
+      <c r="R2" t="str">
         <v>08:00 - 10:00</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
+        <v>1002</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
         <v>Tran Thi B</v>
       </c>
-      <c r="B3" t="str">
+      <c r="D3" t="str">
         <v>079123456789</v>
       </c>
-      <c r="C3" t="str">
+      <c r="E3" t="str">
         <v>tranthib@example.com</v>
       </c>
-      <c r="D3" t="str">
+      <c r="F3" t="str">
         <v>0987654321</v>
       </c>
-      <c r="E3" t="str">
+      <c r="G3" t="str">
         <v>1995-12-01</v>
       </c>
-      <c r="F3" t="str">
+      <c r="H3" t="str">
         <v>F</v>
       </c>
-      <c r="G3" t="str">
+      <c r="I3" t="str">
         <v>Khu B</v>
       </c>
-      <c r="H3" t="str">
-        <v>1002</v>
-      </c>
-      <c r="I3" t="str">
+      <c r="J3" t="str">
         <v>TTB-42K</v>
       </c>
-      <c r="J3" t="str">
+      <c r="K3" t="str">
         <v>42km</v>
       </c>
-      <c r="K3" t="str">
+      <c r="L3" t="str">
         <v>Ao size S</v>
       </c>
-      <c r="L3" t="str">
+      <c r="M3" t="str">
         <v/>
       </c>
-      <c r="M3" t="str">
+      <c r="N3" t="str">
         <v>registered</v>
       </c>
-      <c r="N3" t="str">
+      <c r="O3" t="str">
         <v>import</v>
-      </c>
-      <c r="O3" t="str">
-        <v/>
       </c>
       <c r="P3" t="str">
         <v/>
@@ -577,17 +584,20 @@
       <c r="Q3" t="str">
         <v/>
       </c>
+      <c r="R3" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -607,106 +617,117 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>fullname, cccd</v>
+        <v>bib, chip</v>
       </c>
       <c r="B2" t="str">
-        <v>Co</v>
+        <v>Khong</v>
       </c>
       <c r="C2" t="str">
-        <v>Ho ten day du + so giay to (CCCD/CMND).</v>
+        <v>Cot 1-2: BIB, chip RFID (tuong ung participant_checkin_h).</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>dob(yyyy-mm-dd) hoac dob</v>
+        <v>fullname, cccd</v>
       </c>
       <c r="B3" t="str">
-        <v>Khong</v>
+        <v>Co</v>
       </c>
       <c r="C3" t="str">
-        <v>Ngay sinh: chuoi yyyy-mm-dd hoac o Date trong Excel; khong dung text dang dd/mm/yyyy.</v>
+        <v>Ho ten day du + so giay to (CCCD/CMND).</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>gender</v>
+        <v>dob(yyyy-mm-dd) hoac dob</v>
       </c>
       <c r="B4" t="str">
         <v>Khong</v>
       </c>
       <c r="C4" t="str">
-        <v>M hoac F / Nam hoac Nu.</v>
+        <v>Ngay sinh: chuoi yyyy-mm-dd hoac o Date trong Excel; khong dung text dang dd/mm/yyyy.</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>status</v>
+        <v>gender</v>
       </c>
       <c r="B5" t="str">
         <v>Khong</v>
       </c>
       <c r="C5" t="str">
-        <v>pending | registered | checked_in | cancelled. Mac dinh khi import: registered.</v>
+        <v>M hoac F / Nam hoac Nu.</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>checkin_method</v>
+        <v>status</v>
       </c>
       <c r="B6" t="str">
         <v>Khong</v>
       </c>
       <c r="C6" t="str">
-        <v>scan | manual | kiosk | import | app. Mac dinh: import.</v>
+        <v>pending | registered | checked_in | cancelled. Mac dinh khi import: registered.</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>qr_code</v>
+        <v>checkin_method</v>
       </c>
       <c r="B7" t="str">
         <v>Khong</v>
       </c>
       <c r="C7" t="str">
-        <v>De trong: he thong gan bang uid sau khi import.</v>
+        <v>scan | manual | kiosk | import | app. Mac dinh: import.</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>pickup_time_range</v>
+        <v>qr_code</v>
       </c>
       <c r="B8" t="str">
         <v>Khong</v>
       </c>
       <c r="C8" t="str">
-        <v>Chuoi khung gio nhan (vd 08:00 - 10:00).</v>
+        <v>De trong: he thong gan bang uid sau khi import.</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>checkin_time</v>
+        <v>pickup_time_range</v>
       </c>
       <c r="B9" t="str">
         <v>Khong</v>
       </c>
       <c r="C9" t="str">
-        <v>Ngay gio day du: o Excel Date/DateTime hoac chuoi parse duoc.</v>
+        <v>Chuoi khung gio nhan (vd 08:00 - 10:00).</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
+        <v>checkin_time</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Khong</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Ngay gio day du: o Excel Date/DateTime hoac chuoi parse duoc.</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
         <v>Cac cot khac</v>
       </c>
-      <c r="B10" t="str">
-        <v>Khong</v>
-      </c>
-      <c r="C10" t="str">
-        <v>email, phone, zone, bib, bib_name, category, item, checkin_by...</v>
+      <c r="B11" t="str">
+        <v>Khong</v>
+      </c>
+      <c r="C11" t="str">
+        <v>email, phone, zone, bib_name, category, item, checkin_by...</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
   </ignoredErrors>
 </worksheet>
 </file>